--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Methoden-ValueSet für die Mikroskopie: mikroskopische Verfahren einschließlich der eingesetzten Färbetechnik.</t>
+    <t>Methoden-ValueSet für die Mikroskopie: die eingesetzten mikroskopischen Verfahren. Die Färbung wird nicht hier, sondern in der Extension MII_EX_Mikrobio_Faerbung angegeben.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -119,9 +118,6 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>703857004</t>
   </si>
 </sst>
 </file>
@@ -433,56 +429,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
